--- a/artfynd/A 2406-2025 artfynd.xlsx
+++ b/artfynd/A 2406-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136438764</v>
       </c>
       <c r="B2" t="n">
-        <v>99259</v>
+        <v>99262</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 2406-2025 artfynd.xlsx
+++ b/artfynd/A 2406-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136438764</v>
       </c>
       <c r="B2" t="n">
-        <v>99262</v>
+        <v>99263</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 2406-2025 artfynd.xlsx
+++ b/artfynd/A 2406-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136438764</v>
       </c>
       <c r="B2" t="n">
-        <v>99263</v>
+        <v>99268</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 2406-2025 artfynd.xlsx
+++ b/artfynd/A 2406-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136438764</v>
       </c>
       <c r="B2" t="n">
-        <v>99268</v>
+        <v>99270</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 2406-2025 artfynd.xlsx
+++ b/artfynd/A 2406-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136438764</v>
       </c>
       <c r="B2" t="n">
-        <v>99270</v>
+        <v>99276</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 2406-2025 artfynd.xlsx
+++ b/artfynd/A 2406-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136438764</v>
       </c>
       <c r="B2" t="n">
-        <v>99276</v>
+        <v>99278</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 2406-2025 artfynd.xlsx
+++ b/artfynd/A 2406-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136438764</v>
       </c>
       <c r="B2" t="n">
-        <v>99278</v>
+        <v>99279</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
